--- a/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Заказ ЛП Луганск 130133073.xlsx
+++ b/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Заказ ЛП Луганск 130133073.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино ЗПФ\ostankino_zpf\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0F8A16-7156-4443-B66E-054AB4C7CE0C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EFD848-F7EB-439C-92E9-93DFFEB61AF5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$23</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$448</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$448</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$455</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$455</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -150,6 +150,27 @@
   </si>
   <si>
     <t>Луганск</t>
+  </si>
+  <si>
+    <t>ОСТАНКИНСКИЕ пельм кор.0.5кг зам_NEW</t>
+  </si>
+  <si>
+    <t>С КАРТОФ.И ГРИБ.вареники пл.0.42кг зам.</t>
+  </si>
+  <si>
+    <t>ОСТАНКИНСКИЕ пельм пл. 0.7кг 10шт.зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм пл.0.42кг зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм пл.0.7кг зам.</t>
+  </si>
+  <si>
+    <t>МЯСНЫЕ ПРЕМИУМ пельм кор.0.4кг зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм 4кг зам.</t>
   </si>
 </sst>
 </file>
@@ -284,7 +305,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -332,20 +353,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="lightHorizontal">
-        <fgColor indexed="42"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -530,30 +539,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="57"/>
-      </left>
-      <right style="double">
-        <color indexed="57"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -568,7 +553,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -714,20 +699,20 @@
     <xf numFmtId="2" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -737,26 +722,8 @@
     <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="1" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -765,88 +732,7 @@
     <cellStyle name="Обычный 13" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1241,7 +1127,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K1538"/>
+  <dimension ref="A1:K1545"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -1280,13 +1166,13 @@
       <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="55">
+      <c r="D3" s="52">
         <v>46209</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="55">
+      <c r="F3" s="52">
         <f>D3+3</f>
         <v>46212</v>
       </c>
@@ -1400,7 +1286,8 @@
       <c r="J11" s="42"/>
     </row>
     <row r="12" spans="1:11" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="60">
+      <c r="A12" s="53" t="str">
+        <f>RIGHT(D12,4)</f>
         <v>5897</v>
       </c>
       <c r="B12" s="49" t="s">
@@ -1429,7 +1316,8 @@
       <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="60">
+      <c r="A13" s="53" t="str">
+        <f t="shared" ref="A13:A30" si="0">RIGHT(D13,4)</f>
         <v>6149</v>
       </c>
       <c r="B13" s="49" t="s">
@@ -1446,7 +1334,7 @@
         <v>0.3</v>
       </c>
       <c r="G13" s="22">
-        <f t="shared" ref="G13:G19" si="0">E13*F13</f>
+        <f t="shared" ref="G13:G19" si="1">E13*F13</f>
         <v>0</v>
       </c>
       <c r="H13" s="14">
@@ -1458,7 +1346,8 @@
       <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="60">
+      <c r="A14" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6819</v>
       </c>
       <c r="B14" s="49" t="s">
@@ -1475,7 +1364,7 @@
         <v>0.3</v>
       </c>
       <c r="G14" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
@@ -1487,7 +1376,8 @@
       <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="60">
+      <c r="A15" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6202</v>
       </c>
       <c r="B15" s="49" t="s">
@@ -1504,7 +1394,7 @@
         <v>0.3</v>
       </c>
       <c r="G15" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H15" s="14">
@@ -1516,7 +1406,8 @@
       <c r="J15" s="28"/>
     </row>
     <row r="16" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="60">
+      <c r="A16" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6148</v>
       </c>
       <c r="B16" s="49" t="s">
@@ -1533,7 +1424,7 @@
         <v>0.3</v>
       </c>
       <c r="G16" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H16" s="14">
@@ -1545,7 +1436,8 @@
       <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="60">
+      <c r="A17" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6209</v>
       </c>
       <c r="B17" s="49" t="s">
@@ -1562,7 +1454,7 @@
         <v>0.35</v>
       </c>
       <c r="G17" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H17" s="14">
@@ -1574,7 +1466,8 @@
       <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="60">
+      <c r="A18" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6168</v>
       </c>
       <c r="B18" s="49" t="s">
@@ -1591,7 +1484,7 @@
         <v>0.35</v>
       </c>
       <c r="G18" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H18" s="14">
@@ -1603,7 +1496,8 @@
       <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="60">
+      <c r="A19" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>5579</v>
       </c>
       <c r="B19" s="49" t="s">
@@ -1620,7 +1514,7 @@
         <v>0.42</v>
       </c>
       <c r="G19" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H19" s="14">
@@ -1632,10 +1526,11 @@
       <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="61">
+      <c r="A20" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>5754</v>
       </c>
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="54" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="47" t="s">
@@ -1648,7 +1543,7 @@
       <c r="F20" s="22">
         <v>4.5</v>
       </c>
-      <c r="G20" s="63">
+      <c r="G20" s="55">
         <f>E20</f>
         <v>0</v>
       </c>
@@ -1661,7 +1556,8 @@
       <c r="J20" s="28"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="61">
+      <c r="A21" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>5755</v>
       </c>
       <c r="B21" s="49" t="s">
@@ -1677,7 +1573,7 @@
       <c r="F21" s="22">
         <v>4.5</v>
       </c>
-      <c r="G21" s="63">
+      <c r="G21" s="55">
         <f>E21</f>
         <v>0</v>
       </c>
@@ -1689,22 +1585,23 @@
       </c>
       <c r="J21" s="28"/>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="53"/>
-      <c r="B22" s="64" t="s">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="51"/>
+      <c r="B22" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-    </row>
-    <row r="23" spans="1:10" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="65">
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+    </row>
+    <row r="23" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>7216</v>
       </c>
       <c r="B23" s="54" t="s">
@@ -1713,112 +1610,224 @@
       <c r="C23" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="66">
+      <c r="D23" s="48">
         <v>1002116437216</v>
       </c>
-      <c r="E23" s="51"/>
+      <c r="E23" s="23"/>
       <c r="F23" s="22">
         <v>0.7</v>
       </c>
-      <c r="G23" s="63">
+      <c r="G23" s="55">
         <f>E23*F23</f>
         <v>0</v>
       </c>
       <c r="H23" s="14"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="52"/>
-    </row>
-    <row r="24" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="50"/>
-      <c r="B24" s="44" t="s">
+      <c r="I23" s="14"/>
+      <c r="J23" s="28"/>
+    </row>
+    <row r="24" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>6824</v>
+      </c>
+      <c r="B24" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="48">
+        <v>1002112606824</v>
+      </c>
+      <c r="E24" s="23"/>
+      <c r="F24" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="55">
+        <f t="shared" ref="G24:G29" si="2">E24*F24</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="28"/>
+    </row>
+    <row r="25" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7049</v>
+      </c>
+      <c r="B25" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="48">
+        <v>1002151787049</v>
+      </c>
+      <c r="E25" s="23"/>
+      <c r="F25" s="22">
+        <v>0.42</v>
+      </c>
+      <c r="G25" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="28"/>
+    </row>
+    <row r="26" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7085</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="48">
+        <v>1002112607085</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="G26" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="28"/>
+    </row>
+    <row r="27" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7212</v>
+      </c>
+      <c r="B27" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="48">
+        <v>1002112857212</v>
+      </c>
+      <c r="E27" s="23"/>
+      <c r="F27" s="22">
+        <v>0.42</v>
+      </c>
+      <c r="G27" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="28"/>
+    </row>
+    <row r="28" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7214</v>
+      </c>
+      <c r="B28" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="48">
+        <v>1002112857214</v>
+      </c>
+      <c r="E28" s="23"/>
+      <c r="F28" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="G28" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="28"/>
+    </row>
+    <row r="29" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7224</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="48">
+        <v>1002116517224</v>
+      </c>
+      <c r="E29" s="23"/>
+      <c r="F29" s="22">
+        <v>0.4</v>
+      </c>
+      <c r="G29" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="28"/>
+    </row>
+    <row r="30" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7375</v>
+      </c>
+      <c r="B30" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="48">
+        <v>1002112857375</v>
+      </c>
+      <c r="E30" s="23"/>
+      <c r="F30" s="22">
+        <v>1</v>
+      </c>
+      <c r="G30" s="55">
+        <f>E30</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="28"/>
+    </row>
+    <row r="31" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="50"/>
+      <c r="B31" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="16">
-        <f>SUM(E10:E23)</f>
+      <c r="C31" s="15"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="16">
+        <f>SUM(E10:E30)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16">
-        <f>SUM(G12:G23)</f>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16">
+        <f>SUM(G10:G30)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="35"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="38"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="20"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="35"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="38"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="20"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="35"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="38"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="20"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="35"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="38"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="20"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="35"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="38"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="20"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="35"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="38"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="20"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="35"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="38"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="20"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B32" s="35"/>
       <c r="C32" s="17"/>
       <c r="D32" s="38"/>
@@ -16868,13 +16877,83 @@
       <c r="I1536" s="19"/>
       <c r="J1536" s="20"/>
     </row>
-    <row r="1537" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="1537" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B1537" s="35"/>
       <c r="C1537" s="17"/>
-    </row>
-    <row r="1538" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="D1537" s="38"/>
+      <c r="F1537" s="18"/>
+      <c r="G1537" s="18"/>
+      <c r="H1537" s="19"/>
+      <c r="I1537" s="19"/>
+      <c r="J1537" s="20"/>
+    </row>
+    <row r="1538" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B1538" s="35"/>
       <c r="C1538" s="17"/>
+      <c r="D1538" s="38"/>
+      <c r="F1538" s="18"/>
+      <c r="G1538" s="18"/>
+      <c r="H1538" s="19"/>
+      <c r="I1538" s="19"/>
+      <c r="J1538" s="20"/>
+    </row>
+    <row r="1539" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1539" s="35"/>
+      <c r="C1539" s="17"/>
+      <c r="D1539" s="38"/>
+      <c r="F1539" s="18"/>
+      <c r="G1539" s="18"/>
+      <c r="H1539" s="19"/>
+      <c r="I1539" s="19"/>
+      <c r="J1539" s="20"/>
+    </row>
+    <row r="1540" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1540" s="35"/>
+      <c r="C1540" s="17"/>
+      <c r="D1540" s="38"/>
+      <c r="F1540" s="18"/>
+      <c r="G1540" s="18"/>
+      <c r="H1540" s="19"/>
+      <c r="I1540" s="19"/>
+      <c r="J1540" s="20"/>
+    </row>
+    <row r="1541" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1541" s="35"/>
+      <c r="C1541" s="17"/>
+      <c r="D1541" s="38"/>
+      <c r="F1541" s="18"/>
+      <c r="G1541" s="18"/>
+      <c r="H1541" s="19"/>
+      <c r="I1541" s="19"/>
+      <c r="J1541" s="20"/>
+    </row>
+    <row r="1542" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1542" s="35"/>
+      <c r="C1542" s="17"/>
+      <c r="D1542" s="38"/>
+      <c r="F1542" s="18"/>
+      <c r="G1542" s="18"/>
+      <c r="H1542" s="19"/>
+      <c r="I1542" s="19"/>
+      <c r="J1542" s="20"/>
+    </row>
+    <row r="1543" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1543" s="35"/>
+      <c r="C1543" s="17"/>
+      <c r="D1543" s="38"/>
+      <c r="F1543" s="18"/>
+      <c r="G1543" s="18"/>
+      <c r="H1543" s="19"/>
+      <c r="I1543" s="19"/>
+      <c r="J1543" s="20"/>
+    </row>
+    <row r="1544" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1544" s="35"/>
+      <c r="C1544" s="17"/>
+    </row>
+    <row r="1545" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1545" s="35"/>
+      <c r="C1545" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A9:J23" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -16883,16 +16962,6 @@
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="B22:J22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="17" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
